--- a/Templates/Template_X-1.12_ADR_Deroga_a_una_regola_della_metodologia.xlsx
+++ b/Templates/Template_X-1.12_ADR_Deroga_a_una_regola_della_metodologia.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="X-1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'X-1'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'X-1'!$A$1:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -180,15 +180,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -554,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -572,28 +571,28 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="39" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Template ARCADIA per i team di sviluppo · v1.1 · 27/10/2026 · Baseline delle specifiche: SUBSET-026 v3.6.0 (B3R2) · Chi compila: chi propone la decisione (team o Design Authority) · Quando serve, in qualunque passo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17" customHeight="1">
+          <t>Template ARCADIA per i team di sviluppo · v1.1 · 30/10/2026 · Baseline delle specifiche: SUBSET-026 v3.6.0 (B3R2) · Chi compila: chi propone la decisione (team o Design Authority) · Quando serve, in qualunque passo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Scopo. Una regola della metodologia non viene rispettata, consapevolmente e con una motivazione.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="39" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Come si compila. In ATLAS si crea con «Nuova ADR» e il tipo «Deroga a una regola della metodologia»: la scheda ha gli stessi campi di questo template. La data della decisione è quella in cui la Design Authority decide (la DA è sempre il decisore).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>Come si compila. In ATLAS si crea con «Nuova ADR» e il tipo «Deroga a una regola della metodologia»: la scheda ha gli stessi campi di questo template. La data della decisione è quella in cui la Design Authority decide (la DA è sempre il decisore); l'esito e le osservazioni della DA sono nella sezione «Decisione della DA».</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Legenda: le celle bianche vanno compilate; il testo grigio in corsivo è guida o esempio del template e va sostituito. Le celle «Stato» e le colonne a valori fissi propongono un elenco a tendina.</t>
@@ -638,13 +637,13 @@
           <t>Autore</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr"/>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Revisore</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Data</t>
@@ -656,7 +655,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="31" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Stato</t>
@@ -682,21 +681,21 @@
           <t>Rif. Capella / DOORS</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Identificazione</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="12" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>ID e titolo</t>
@@ -707,12 +706,12 @@
           <t>ADR-nnn · titolo della decisione</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Tipo di decisione</t>
@@ -723,12 +722,12 @@
           <t>Deroga a una regola della metodologia</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="12" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Stato</t>
@@ -736,15 +735,15 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Proposta / Decisa / Superata</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="12" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
+          <t>Proposta / In revisione DA / Revisionato DA / Decisa / Superata</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Superata da</t>
@@ -755,12 +754,12 @@
           <t>es. ADR-nnn</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="12" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Proponente (team)</t>
@@ -771,294 +770,349 @@
           <t>es. T5 · Odometria</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>Proponente (membro del team)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Uno dei membri del team proponente: es. Anna Bianchi</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>Data della decisione</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>gg/mm/aaaa · impostata da ATLAS quando la Design Authority decide</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="12" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Dettagli: Deroga a una regola della metodologia</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="12" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="41" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Regola o controllo derogato (es. SA2-07)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="12" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="12" t="n"/>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Contesto</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Il problema e perché va deciso ora</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="12" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Voci SRS interessate</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Uno o più: es. 3.14.4.2</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="12" t="n"/>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Altri elementi del modello interessati</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="12" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Opzioni</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="12" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Opzione</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Vantaggi</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Svantaggi e rischi</t>
         </is>
       </c>
-      <c r="F27" s="12" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="12" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="12" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="12" t="n"/>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Decisione</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="11" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="10" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="11" t="n"/>
-      <c r="F33" s="12" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Motivazione</t>
+          <t>Decisione</t>
         </is>
       </c>
       <c r="B34" s="7" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="12" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Conseguenze</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Cosa cambia nel modello, nei requisiti, nei test</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="12" t="n"/>
+          <t>Motivazione</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>Conseguenze</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Cosa cambia nel modello, nei requisiti, nei test</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>Da rivedere quando</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Condizione che riapre la decisione, se esiste</t>
         </is>
       </c>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="12" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Decisione della DA</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Esito della decisione DA</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Commenti DA / Accolta / Accolta con modifiche / Respinta</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Osservazioni DA</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="39">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B25:F25"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="B23:F23"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bozza,In revisione,Approvato"</formula1>
     </dataValidation>
     <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Proposta,Decisa,Superata"</formula1>
+      <formula1>"Proposta,In revisione DA,Revisionato DA,Decisa,Superata"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Commenti DA,Accolta,Accolta con modifiche,Respinta"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 Informazione ad uso interno - Internal use information&amp;R&amp;8 &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>